--- a/app/parsers/LDR_clean.xlsx
+++ b/app/parsers/LDR_clean.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OqT70qCIobR7b2fj2vyX6rXc0SUvYtGZIUvkBZKn3wQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="9DASDf+mFuvUdNgMYlOCosrBPiTsysTG/lNxUIISxn8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7099" uniqueCount="2863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7100" uniqueCount="2863">
   <si>
     <t>300</t>
   </si>
@@ -8859,7 +8859,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="337" width="8.71"/>
+    <col customWidth="1" min="1" max="338" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9873,6 +9873,9 @@
       </c>
       <c r="LY1" s="1" t="s">
         <v>336</v>
+      </c>
+      <c r="LZ1" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2">
